--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -742,7 +733,7 @@
         <v>33.5</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>21.6</v>
@@ -754,22 +745,22 @@
         <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
@@ -780,11 +771,11 @@
       <c r="Q4" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>11.3</v>
+        <v>4.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
@@ -817,10 +808,10 @@
       <c r="E5" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -833,17 +824,17 @@
         <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="n">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>9.1</v>
@@ -858,9 +849,9 @@
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U5" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="V5" s="3" t="n">
@@ -870,10 +861,10 @@
         <v>13.3</v>
       </c>
       <c r="X5" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y5" s="3" t="n">
         <v>16.8</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>96.8</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>32.2</v>
@@ -903,8 +894,8 @@
       <c r="F6" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>23.9</v>
+      <c r="G6" s="3" t="n">
+        <v>23.1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -926,15 +917,15 @@
       </c>
       <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="8" t="n">
+      <c r="R6" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -959,7 +950,7 @@
         <v>21.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>230.2</v>
+        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -986,7 +977,7 @@
       <c r="F7" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -999,7 +990,7 @@
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
@@ -1008,7 +999,7 @@
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>35</v>
@@ -1019,11 +1010,11 @@
       <c r="Q7" s="3" t="n">
         <v>34.7</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>14.4</v>
@@ -1038,10 +1029,10 @@
         <v>13.5</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>33.4</v>
@@ -1080,7 +1071,7 @@
       <c r="I8" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="K8" s="3" t="n">
@@ -1102,7 +1093,7 @@
       <c r="Q8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1112,12 +1103,12 @@
         <v>6.6</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>21.7</v>
+        <v>31.7</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="W8" s="8" t="n">
+      <c r="W8" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1143,16 +1134,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2636.1</v>
+        <v>2656</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>169.7</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>123.3</v>
+        <v>33.3</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1113.4</v>
+        <v>111.4</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>116.4</v>
@@ -1167,10 +1158,10 @@
         <v>68.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>167.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>32.5</v>
@@ -1179,40 +1170,40 @@
         <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1183</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>48.7</v>
+        <v>49.7</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>165</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>171.8</v>
+        <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.7</v>
+        <v>27.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>224.8</v>
+        <v>224.1</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>139.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>169.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>8.9</v>
+        <v>18.9</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>120.2</v>
+        <v>20.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1231,19 +1222,19 @@
         <v>531.2</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>10.2</v>
+        <v>33.9</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>47.8</v>
+      <c r="H10" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1283,14 +1274,14 @@
       <c r="V10" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="8" t="n">
-        <v>19.9</v>
+      <c r="W10" s="3" t="n">
+        <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>38.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1106.2</v>
+        <v>106.2</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>21.2</v>
@@ -1312,13 +1303,13 @@
         <v>427.9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>30.8</v>
+        <v>30.3</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>83.8</v>
+        <v>23.9</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>13.3</v>
@@ -1326,14 +1317,14 @@
       <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I11" s="8" t="n">
-        <v>46.9</v>
+      <c r="I11" s="3" t="n">
+        <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
@@ -1342,7 +1333,7 @@
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>13</v>
@@ -1362,14 +1353,14 @@
       <c r="T11" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="U11" s="8" t="n">
+      <c r="U11" s="3" t="n">
         <v>31</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>14</v>
+      <c r="W11" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
@@ -1394,10 +1385,10 @@
         <v>31.1</v>
       </c>
       <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1419,13 +1410,13 @@
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="P12" s="8" t="n">
-        <v>20</v>
+      <c r="P12" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>31.3</v>
@@ -1439,17 +1430,17 @@
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="U12" s="8" t="n">
-        <v>29.2</v>
+      <c r="U12" s="3" t="n">
+        <v>39.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>27</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X12" s="8" t="n">
-        <v>2.3</v>
+        <v>15.1</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>47</v>
@@ -1485,7 +1476,7 @@
       <c r="G13" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I13" s="3" t="n">
@@ -1513,8 +1504,8 @@
       <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>15.8</v>
+      <c r="R13" s="3" t="n">
+        <v>15.3</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1522,8 +1513,8 @@
       <c r="T13" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="U13" s="8" t="n">
-        <v>49</v>
+      <c r="U13" s="3" t="n">
+        <v>44</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>28.7</v>
@@ -1554,13 +1545,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>24.6</v>
@@ -1583,8 +1574,8 @@
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="8" t="n">
-        <v>22</v>
+      <c r="M14" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
@@ -1593,10 +1584,10 @@
       <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="8" t="n">
+      <c r="R14" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1605,8 +1596,8 @@
       <c r="T14" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U14" s="8" t="n">
-        <v>236</v>
+      <c r="U14" s="3" t="n">
+        <v>36</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>27</v>
@@ -1615,13 +1606,13 @@
         <v>14.5</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>114.4</v>
+        <v>14.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1637,18 +1628,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>552.9</v>
+        <v>552.1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1664,29 +1655,29 @@
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M15" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="M15" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>418</v>
+        <v>26.2</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="R15" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>115.4</v>
+        <v>15.4</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>38</v>
@@ -1720,43 +1711,43 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>237.7</v>
+        <v>257.7</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1291.6</v>
+        <v>159.6</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>76.8</v>
+        <v>26.8</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>2118.2</v>
+        <v>118.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>397.3</v>
+        <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>136.2</v>
+        <v>36.2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>880.9</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>212.5</v>
+        <v>218.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
@@ -1765,13 +1756,13 @@
         <v>154.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>173.6</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>188.2</v>
@@ -1780,16 +1771,16 @@
         <v>131.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1145.8</v>
+        <v>145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1224.4</v>
+        <v>124.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1805,10 +1796,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>315.4</v>
+        <v>515.4</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>21.9</v>
+        <v>31.9</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>13.4</v>
@@ -1816,14 +1807,14 @@
       <c r="F17" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="G17" s="8" t="n">
-        <v>18.5</v>
+      <c r="G17" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>11.2</v>
@@ -1834,11 +1825,11 @@
       <c r="L17" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>42.5</v>
@@ -1864,11 +1855,11 @@
       <c r="V17" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W17" s="8" t="n">
+      <c r="W17" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>29.2</v>
@@ -1890,12 +1881,12 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>252.1</v>
+        <v>352.1</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="E18" s="8" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="F18" s="3" t="n">
@@ -1914,23 +1905,23 @@
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="8" t="n">
-        <v>18.5</v>
+      <c r="L18" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>137.5</v>
+        <v>37.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q18" s="8" t="n">
-        <v>29.1</v>
+      <c r="Q18" s="3" t="n">
+        <v>32.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>15.2</v>
@@ -1939,16 +1930,16 @@
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>115.5</v>
+        <v>15.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>10.4</v>
+        <v>40.4</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="W18" s="8" t="n">
-        <v>84.40000000000001</v>
+      <c r="W18" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>8.4</v>
@@ -1957,7 +1948,7 @@
         <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.2</v>
+        <v>29.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1964,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.4</v>
+        <v>526.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>33.4</v>
@@ -1993,8 +1984,8 @@
       <c r="I19" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J19" s="8" t="n">
-        <v>20.6</v>
+      <c r="J19" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
@@ -2009,7 +2000,7 @@
         <v>0.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>6</v>
@@ -2029,14 +2020,14 @@
       <c r="U19" s="3" t="n">
         <v>41.4</v>
       </c>
-      <c r="V19" s="8" t="n">
+      <c r="V19" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>19</v>
@@ -2067,7 +2058,7 @@
         <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>20.3</v>
+        <v>24.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2082,16 +2073,16 @@
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="L20" s="8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>55</v>
@@ -2117,7 +2108,7 @@
       <c r="V20" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2127,7 +2118,7 @@
         <v>32</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>118.2</v>
+        <v>18.2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2143,12 +2134,12 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>42.2</v>
+        <v>542.2</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="F21" s="3" t="n">
@@ -2158,7 +2149,7 @@
         <v>14.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
@@ -2179,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.3</v>
@@ -2194,7 +2185,7 @@
         <v>7.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>117.2</v>
+        <v>17.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>36.6</v>
@@ -2248,20 +2239,20 @@
       <c r="I22" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="J22" s="8" t="n">
+      <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" s="3" t="n">
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.9</v>
+        <v>9.6</v>
       </c>
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="n">
@@ -2277,13 +2268,13 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="U22" s="8" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U22" s="3" t="n">
         <v>39</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>14.6</v>
@@ -2311,13 +2302,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2517.5</v>
+        <v>2547.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>160.3</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>117.1</v>
@@ -2326,7 +2317,7 @@
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>160</v>
+        <v>22.2</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
@@ -2344,13 +2335,13 @@
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>154.4</v>
@@ -2369,10 +2360,10 @@
         <v>130.5</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>168.8</v>
+        <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>142.8</v>
+        <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
@@ -2421,7 +2412,7 @@
         <v>0.1</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>13.8</v>
+        <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>10.1</v>
@@ -2430,7 +2421,7 @@
         <v>0.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>294.6</v>
+        <v>54.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
@@ -2460,10 +2451,10 @@
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>23.5</v>
+        <v>25.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2479,18 +2470,18 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>45.5</v>
+        <v>455.5</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>21.9</v>
+        <v>31.9</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F25" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G25" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2508,7 +2499,7 @@
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2517,38 +2508,38 @@
       <c r="O25" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="P25" s="8" t="n">
-        <v>14.8</v>
+      <c r="P25" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>11.4</v>
+        <v>1.1</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="S25" s="8" t="n">
+      <c r="S25" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v>26.2</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="W25" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>457.3</v>
+        <v>45.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2569,17 +2560,17 @@
       <c r="D26" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>2.8</v>
+        <v>13.5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>21.6</v>
+        <v>11.6</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>7.3</v>
@@ -2597,10 +2588,10 @@
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
@@ -2612,25 +2603,25 @@
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="U26" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="W26" s="8" t="n">
+      <c r="W26" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>19.4</v>
+        <v>9.4</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>222</v>
+        <v>27</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>25</v>
@@ -2657,7 +2648,7 @@
       <c r="E27" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F27" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="G27" s="3" t="n">
@@ -2667,7 +2658,7 @@
         <v>12.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>10.4</v>
@@ -2682,10 +2673,10 @@
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>9.9</v>
@@ -2693,14 +2684,14 @@
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="8" t="n">
+      <c r="R27" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>37.4</v>
@@ -2712,10 +2703,10 @@
         <v>14.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>126.6</v>
+        <v>26.6</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>26.3</v>
@@ -2739,23 +2730,23 @@
       <c r="D28" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E28" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="8" t="n">
-        <v>18.1</v>
+      <c r="G28" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10.4</v>
+        <v>20.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>11</v>
+        <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
@@ -2767,12 +2758,12 @@
         <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="P28" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="P28" s="3" t="n">
         <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
@@ -2782,13 +2773,13 @@
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>598.4</v>
+        <v>19.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>27.7</v>
@@ -2827,11 +2818,11 @@
       <c r="E29" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>38.3</v>
+      <c r="F29" s="3" t="n">
+        <v>23.3</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.6</v>
@@ -2852,7 +2843,7 @@
         <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>41.3</v>
@@ -2863,16 +2854,16 @@
       <c r="Q29" s="3" t="n">
         <v>33.5</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="U29" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U29" s="3" t="n">
         <v>47.1</v>
       </c>
       <c r="V29" s="3" t="n">
@@ -2888,7 +2879,7 @@
         <v>18.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2904,7 +2895,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2781.9</v>
+        <v>271.9</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>161.6</v>
@@ -2922,19 +2913,19 @@
         <v>57</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>237</v>
+        <v>37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>135.8</v>
+        <v>35.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>18.9</v>
+        <v>10.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>30.6</v>
+        <v>50.6</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>4.3</v>
@@ -2943,19 +2934,19 @@
         <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>91.7</v>
+        <v>51.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>153.1</v>
+        <v>155.1</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>20.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>22.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>194.1</v>
@@ -2987,7 +2978,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>336.4</v>
+        <v>556.4</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>32.3</v>
@@ -3007,23 +2998,23 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="8" t="n">
+      <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0.8</v>
+        <v>8.1</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
-      <c r="P31" s="8" t="n">
+      <c r="P31" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="Q31" s="3" t="n">
@@ -3033,7 +3024,7 @@
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>2</v>
+        <v>6.2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3051,10 +3042,10 @@
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>127.3</v>
+        <v>27.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3070,7 +3061,7 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>208.6</v>
+        <v>611.1</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>33.8</v>
@@ -3092,16 +3083,16 @@
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>16</v>
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
@@ -3116,16 +3107,16 @@
         <v>14.1</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>14.7</v>
+        <v>4.7</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>1141.1</v>
+        <v>1.4</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>484.1</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>90.8</v>
+        <v>9</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>28.5</v>
@@ -3151,25 +3142,25 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>443.7</v>
+        <v>243.7</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>31.2</v>
       </c>
-      <c r="E33" s="8" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F33" s="8" t="n">
+      <c r="E33" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F33" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G33" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
@@ -3177,7 +3168,7 @@
       <c r="K33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L33" s="8" t="n">
+      <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3195,7 +3186,7 @@
       <c r="Q33" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="R33" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3204,23 +3195,23 @@
       <c r="T33" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="U33" s="8" t="n">
-        <v>83.40000000000001</v>
+      <c r="U33" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="X33" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1420.9</v>
+        <v>22.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>113.9</v>
+        <v>13.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3247,14 +3238,14 @@
       <c r="F34" s="3" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G34" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3269,10 +3260,10 @@
         <v>11.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>22.2</v>
+        <v>32.2</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3287,22 +3278,22 @@
         <v>12.1</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>25.9</v>
+        <v>15</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="X34" s="8" t="n">
-        <v>11.8</v>
+      <c r="X34" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>18.6</v>
@@ -3332,17 +3323,17 @@
       <c r="F35" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G35" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>47.1</v>
@@ -3354,22 +3345,22 @@
         <v>12.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>58.9</v>
+        <v>30.3</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>22.8</v>
@@ -3384,7 +3375,7 @@
         <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>0.2</v>
@@ -3415,10 +3406,10 @@
         <v>11.2</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G36" s="8" t="n">
-        <v>4.8</v>
+        <v>18.3</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>14.3</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>11.2</v>
@@ -3440,7 +3431,7 @@
         <v>1.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3458,22 +3449,22 @@
         <v>34.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="8" t="n">
-        <v>80.59999999999999</v>
+      <c r="X36" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>146.6</v>
+        <v>20.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>126.8</v>
+        <v>16.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3492,10 +3483,10 @@
         <v>2216.6</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>131.6</v>
+        <v>151.6</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>168.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>110.3</v>
@@ -3504,7 +3495,7 @@
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>55.8</v>
+        <v>35.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
@@ -3516,47 +3507,47 @@
         <v>36.1</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>153.2</v>
+        <v>53.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>44.7</v>
+        <v>4.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>2409.2</v>
+        <v>240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>359.5</v>
+        <v>39.3</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>13.3</v>
+        <v>133.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>147.8</v>
+        <v>47.9</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>171.6</v>
+        <v>151.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1141.1</v>
+        <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>188.2</v>
+        <v>187.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3575,41 +3566,43 @@
         <v>443.3</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E38" s="8" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E38" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G38" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="8" t="n">
+      <c r="K38" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>1.5</v>
+        <v>7.9</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>26.7</v>
@@ -3621,12 +3614,12 @@
         <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="U38" s="8" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V38" s="8" t="n">
+      <c r="V38" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W38" s="3" t="n">
@@ -3655,7 +3648,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5914.6</v>
+        <v>514.6</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>29.2</v>
@@ -3663,35 +3656,35 @@
       <c r="E39" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>158</v>
-      </c>
-      <c r="M39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>0.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3706,9 +3699,9 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="U39" s="8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="U39" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="V39" s="3" t="n">
@@ -3751,10 +3744,10 @@
       <c r="F40" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="8" t="n">
+      <c r="H40" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
@@ -3773,10 +3766,10 @@
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>21.7</v>
+        <v>2.2</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3794,22 +3787,22 @@
         <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v>268</v>
+        <v>34.2</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>26</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X40" s="8" t="n">
+      <c r="X40" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>318</v>
+        <v>30</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>223.6</v>
+        <v>23.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3833,14 +3826,14 @@
       <c r="E41" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="F41" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G41" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>53</v>
+      <c r="H41" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>6.6</v>
@@ -3851,19 +3844,19 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="8" t="n">
+      <c r="L41" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>11.1</v>
+        <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="P41" s="8" t="n">
+      <c r="P41" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="Q41" s="3" t="n">
@@ -3878,7 +3871,7 @@
       <c r="T41" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="U41" s="8" t="n">
+      <c r="U41" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="V41" s="3" t="n">
@@ -3888,10 +3881,10 @@
         <v>15.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>128.9</v>
+        <v>28.4</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>26.4</v>
@@ -3913,15 +3906,15 @@
         <v>481.1</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>39.2</v>
+        <v>31.2</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F42" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3936,7 +3929,7 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="L42" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M42" s="3" t="n">
@@ -3961,7 +3954,7 @@
         <v>9.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>128.7</v>
+        <v>28.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>24.6</v>
@@ -3970,16 +3963,16 @@
         <v>19</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>123</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>1392</v>
+        <v>52</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.2</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3995,7 +3988,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>234</v>
+        <v>554</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>30.5</v>
@@ -4006,10 +3999,10 @@
       <c r="F43" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G43" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
@@ -4019,7 +4012,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>17.7</v>
@@ -4028,13 +4021,13 @@
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>21.5</v>
+        <v>31.5</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>28.9</v>
@@ -4046,16 +4039,16 @@
         <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>121.8</v>
-      </c>
-      <c r="U43" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="U43" s="3" t="n">
         <v>31.4</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4088,7 +4081,7 @@
       <c r="E44" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4104,7 +4097,7 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>16.6</v>
@@ -4113,27 +4106,27 @@
         <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>1.8</v>
+        <v>18.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>644</v>
-      </c>
-      <c r="P44" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="P44" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="8" t="n">
+      <c r="R44" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>87.8</v>
+        <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>119.2</v>
-      </c>
-      <c r="U44" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>32.8</v>
       </c>
       <c r="V44" s="3" t="n">
@@ -4142,14 +4135,14 @@
       <c r="W44" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>227.9</v>
+      <c r="X44" s="3" t="n">
+        <v>12.9</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>290.8</v>
+        <v>50.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>112.4</v>
+        <v>12.4</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4165,68 +4158,68 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2312.2</v>
+        <v>3312.2</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>188.7</v>
+        <v>185.7</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>113.8</v>
+        <v>13.7</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>910.8</v>
+        <v>91.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>7194.9</v>
+        <v>21.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>52.3</v>
+        <v>32.3</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>101.9</v>
+        <v>101.1</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>1202.9</v>
+        <v>224</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>2.7</v>
+        <v>27</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>226.5</v>
+        <v>296.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2908.4</v>
+        <v>58.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="R45" s="3" t="inlineStr"/>
       <c r="S45" s="3" t="n">
-        <v>182.8</v>
+        <v>23.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>136.9</v>
+        <v>136.4</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>182.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>146.2</v>
+        <v>144.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>286.2</v>
+        <v>86.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>164.7</v>
+        <v>186.2</v>
       </c>
       <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
@@ -4246,39 +4239,41 @@
       <c r="C46" s="3" t="n">
         <v>551.8</v>
       </c>
-      <c r="D46" s="8" t="n">
-        <v>70.59999999999999</v>
+      <c r="D46" s="3" t="n">
+        <v>30.6</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>1.2</v>
+        <v>15.3</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>149.4</v>
+        <v>49.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
@@ -4287,31 +4282,31 @@
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="S46" s="8" t="n">
-        <v>39</v>
+        <v>15</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="U46" s="8" t="n">
-        <v>390.8</v>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W46" s="8" t="n">
+      <c r="U46" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="X46" s="8" t="n">
-        <v>16.8</v>
+      <c r="X46" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>31.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>119.6</v>
+        <v>19.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
